--- a/translations/welsh-translations/xlsx/04-auth-sign-in-failed.xlsx
+++ b/translations/welsh-translations/xlsx/04-auth-sign-in-failed.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD85069F-E995-4692-9658-2216CA3654DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Welsh translations" state="visible" r:id="rId4"/>
+    <sheet name="Welsh translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>Translator notes</t>
   </si>
@@ -52,9 +56,6 @@
     <t>Sign in failed</t>
   </si>
   <si>
-    <t>Methu mewngofnodi</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -83,27 +84,50 @@
   </si>
   <si>
     <t>We could not sign you in. Try again later.</t>
+  </si>
+  <si>
+    <t>There is no Figma link for this content</t>
+  </si>
+  <si>
+    <t>Wedi methu mewngofnodi</t>
+  </si>
+  <si>
+    <t>Doedd dim modd eich mewngofnodi. Rhowch gynnig arall arni.</t>
+  </si>
+  <si>
+    <t>Doedd dim modd adnabod eich cyfrif. Rhowch gynnig arall arni.</t>
+  </si>
+  <si>
+    <t>Does gennych chi ddim hawl i ddefnyddio’r gwasanaeth hwn.</t>
+  </si>
+  <si>
+    <t>Doedd dim modd eich mewngofnodi. Rhowch gynnig arall arni rywbryd eto.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -131,15 +155,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,9 +510,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="35" hidden="1" customWidth="1"/>
@@ -490,49 +520,49 @@
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="1" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="1" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -545,16 +575,16 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
+      <c r="E6" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -563,18 +593,18 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -583,18 +613,18 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -603,18 +633,18 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -623,18 +653,18 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -643,23 +673,23 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F11"/>
+  <autoFilter ref="A5:F11" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/translations/welsh-translations/xlsx/04-auth-sign-in-failed.xlsx
+++ b/translations/welsh-translations/xlsx/04-auth-sign-in-failed.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD85069F-E995-4692-9658-2216CA3654DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Welsh translations" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Welsh translations" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>Translator notes</t>
   </si>
@@ -56,6 +52,9 @@
     <t>Sign in failed</t>
   </si>
   <si>
+    <t>Wedi methu mewngofnodi</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -65,18 +64,27 @@
     <t>We could not sign you in. Try again.</t>
   </si>
   <si>
+    <t>Doedd dim modd eich mewngofnodi. Rhowch gynnig arall arni.</t>
+  </si>
+  <si>
     <t>auth.signInFailed.noUserId</t>
   </si>
   <si>
     <t>We could not identify your account. Try again.</t>
   </si>
   <si>
+    <t>Doedd dim modd adnabod eich cyfrif. Rhowch gynnig arall arni.</t>
+  </si>
+  <si>
     <t>auth.signInFailed.userNotFound</t>
   </si>
   <si>
     <t>You do not have permission to use this service.</t>
   </si>
   <si>
+    <t>Does gennych chi ddim hawl i ddefnyddio’r gwasanaeth hwn.</t>
+  </si>
+  <si>
     <t>auth.signInFailed.invalidService</t>
   </si>
   <si>
@@ -84,21 +92,6 @@
   </si>
   <si>
     <t>We could not sign you in. Try again later.</t>
-  </si>
-  <si>
-    <t>There is no Figma link for this content</t>
-  </si>
-  <si>
-    <t>Wedi methu mewngofnodi</t>
-  </si>
-  <si>
-    <t>Doedd dim modd eich mewngofnodi. Rhowch gynnig arall arni.</t>
-  </si>
-  <si>
-    <t>Doedd dim modd adnabod eich cyfrif. Rhowch gynnig arall arni.</t>
-  </si>
-  <si>
-    <t>Does gennych chi ddim hawl i ddefnyddio’r gwasanaeth hwn.</t>
   </si>
   <si>
     <t>Doedd dim modd eich mewngofnodi. Rhowch gynnig arall arni rywbryd eto.</t>
@@ -107,27 +100,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -155,21 +143,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -510,9 +492,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="35" hidden="1" customWidth="1"/>
@@ -520,49 +502,49 @@
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="3" t="s">
+    <row r="1" ht="24" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="4" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="4" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -575,16 +557,16 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>24</v>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -593,18 +575,18 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -613,18 +595,18 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -633,18 +615,18 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -653,18 +635,18 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -673,23 +655,23 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F11" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:F11"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>